--- a/vibecoding.xlsx
+++ b/vibecoding.xlsx
@@ -117,11 +117,243 @@
       </xdr:spPr>
     </xdr:pic>
   </etc:cellImage>
+  <etc:cellImage>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="ID_AB034D59810546E6B8090D478F91EFAD"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5962650" y="14909800"/>
+          <a:ext cx="5492750" cy="13417550"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+  </etc:cellImage>
+  <etc:cellImage>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="ID_9007E9C07C77434B99BD21BA91A8210E"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5962650" y="17710150"/>
+          <a:ext cx="5683250" cy="13315950"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+  </etc:cellImage>
+  <etc:cellImage>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="ID_A9BAFE5D8A55439995DC98BD6BE7FC44"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5962650" y="21088350"/>
+          <a:ext cx="5848350" cy="13716000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+  </etc:cellImage>
+  <etc:cellImage>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8" name="ID_8CB55B8CEF6F4AC9A38D8AF353DB8794"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5962650" y="25355550"/>
+          <a:ext cx="4648200" cy="13690600"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+  </etc:cellImage>
+  <etc:cellImage>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="9" name="ID_42D4C69B06DB45018FE4A5B9EC5ACAFA"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5962650" y="30556200"/>
+          <a:ext cx="4241800" cy="13246100"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+  </etc:cellImage>
+  <etc:cellImage>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="10" name="ID_CE1FF791048D4A9C9C815BE270F81F3C"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5962650" y="35756850"/>
+          <a:ext cx="4248150" cy="13277850"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+  </etc:cellImage>
+  <etc:cellImage>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="11" name="ID_70BA1EE1FEF1472FB099100E5566212D"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId10"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5962650" y="40957500"/>
+          <a:ext cx="4514850" cy="13455650"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+  </etc:cellImage>
+  <etc:cellImage>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="12" name="ID_0E58F2BB651D4ECFB462F5288FECD91A"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId11"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5962650" y="46158150"/>
+          <a:ext cx="5416550" cy="13404850"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+  </etc:cellImage>
 </etc:cellImages>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
   <si>
     <t>AI记录</t>
   </si>
@@ -204,6 +436,293 @@
 skill_file: "src/skill/代码Review.txt"
 如果你愿意，下一步我可以继续做第二个 click 方法（你指定名字和行为，我直接接着加到分发器里）。</t>
   </si>
+  <si>
+    <t>@e:\GitHubProject\AICodeTools 接下来参照这个项目，编写一个单独的脚本专门控制调用cursor的agent的，对外只需要暴露一个功能：传入文字，等待返回回答即可</t>
+  </si>
+  <si>
+    <t>已按你的要求新增了一个独立脚本，专门调用 Cursor Agent，并且对外只暴露一个函数：
+新文件：src/cursorAgent.ts
+导出函数：askCursorAgent(prompt: string): Promise&lt;string&gt;
+它的行为是：
+传入一段文字 prompt
+内部自动调用 agent --print --output-format text
+阻塞等待结果返回
+返回 AI 的纯文本回答
+内置了超时（120 秒）和常见错误处理（比如未安装 agent）
+我还做了验证：
+npm run compile 已通过
+新文件无 linter 报错
+你现在可以在任何位置这样用：
+import { askCursorAgent } from "./cursorAgent";
+const answer = await askCursorAgent("帮我审查这段代码");
+console.log(answer);
+如果你要，我下一步可以直接帮你把它接到 skillsBank.skillClick 的某个 click 类型上，实现“点技能 -&gt; 调 agent -&gt; 回显结果”。</t>
+  </si>
+  <si>
+    <t>当然，接下来需要变成这样，在我点击@skills-config.json (2-6) 代码Review按钮的时候打开的窗口里面使用读取到的skill_file对AI发送里面的文字，然后在下方添加一个文本框用于显示AI的回答</t>
+  </si>
+  <si>
+    <t>已完成，代码Review（show_window）现在会按你说的流程工作：
+点击 skills-config.json 里这个技能项后，打开 Webview 窗口
+自动读取 skill_file（即 src/skill/代码Review.txt）内容
+自动把这段文本发送给 Cursor Agent（通过 askCursorAgent）
+在窗口下方新增了一个只读文本框显示 AI 回答
+同时有状态提示：请求中 / 完成 / 失败
+本次改动文件：
+src/extension.ts
+引入 askCursorAgent
+showSkillWindow 改为 enableScripts: true
+页面新增“AI 回答”文本框与状态区域
+Webview 通过 postMessage 请求 AI，扩展侧调用 Agent 后再回传结果
+并且已经验证：
+npm run compile 通过
+无新增 linter 报错
+你现在可以直接 F5 启动调试后点击 代码Review 测试。</t>
+  </si>
+  <si>
+    <t>当前 Cursor 模型在你所在地区不可用。
+已自动将 skill_file 内容复制到剪贴板。
+你可以：
+1) 在 Cursor 设置里切换到当前地区可用模型后重试；
+2) 访问 https://cursor.com/docs/account/regions 查看可用区域与模型；
+3) 将剪贴板内容手动粘贴到你可用的 AI 通道继续使用。
+原始错误：S: Model not available This model provider doesn't serve your region. Visit https://cursor.com/docs/account/regions for more information.？？？？为什么？我代码选择的模型是什么</t>
+  </si>
+  <si>
+    <t>你这个问题问得很对，结论是：
+你的代码没有手动指定模型。
+现在实际使用的是 Cursor Agent 的默认模型，不是你代码里写死的。
+在你的实现里，命令参数只有这些，没有 --model：
+cursorAgent.ts
+Lines 10-13
+function createAgentCommand(prompt: string): { cmd: string; args: string[] } {
+  const workspacePath = process.cwd();
+  const argv = ["--trust", "--print", "--output-format", "text", "--workspace", workspacePath, prompt];
+我刚帮你查了本机 Agent 当前状态，显示：
+当前默认模型：claude-4.6-opus-high-thinking（Opus 4.6 1M Thinking）
+所以你看到的区域报错，不是扩展逻辑错，而是当前默认模型对应的 provider 在该请求路径下被判定为区域不可用（可能是账号区域策略、网络出口地区、或 provider 限制）。
+如果你想完全可控，下一步我可以直接帮你改成：
+在 cursorAgent.ts 显式加 --model &lt;id&gt;（比如你指定一个可用模型）
+或做“主模型失败自动切换备选模型”机制（比如先 A，失败后 B）
+你点头我就直接改。</t>
+  </si>
+  <si>
+    <t>现在，本项目最大的问题来了，你应该知道，与AI对话操作文件 或者解答问题，流程是：选择文件-&gt;描述需求-&gt;等待回答，那么窗口都是统一一样的了，只需要一个mainwindow，然后通过配置选择不同的组件组成窗口内容，比如选项A选择文件使用组件free自由选择，可以通过@的方式或者是拖入文件的方式（哪个好实现用哪个），描述需求目前就是根据配置的skill_file来实现不同提示词执行不同技能，等待回答就是直接返回输出了，所以我要做成可以配置文件选择方式的。比如@skills-config.json (2-8) ，第一个方式就是刚刚说的这个，先做第一个选项free自由选择，可以选择多个文件的，选错可以移除</t>
+  </si>
+  <si>
+    <t>已把你说的“统一窗口 + 可配置文件选择组件”先落地了第一个模式：free。
+这次实现的效果（对应你的流程）：
+选择文件：当 file_select_mode: "free" 时，窗口出现“选择文件（可多选）”按钮
+多文件管理：已选文件会展示成列表，可逐个“移除”
+描述需求：继续使用 skill_file 内容作为技能提示词
+等待回答：点击“执行技能”后请求 AI，回答显示在下方文本框
+同时我把发送给 AI 的内容改成：
+skill_file 提示词
+你当前选中的多个文件内容（逐个附带路径和内容）
+这样就符合你要的统一主窗口能力了。
+已修改：
+src/extension.ts
+新增配置字段解析：file_select_mode
+show_window 改为主窗口执行流程
+实现 free 组件：多选文件、去重、移除、执行
+组装最终 prompt（提示词 + 所选文件内容）
+编译和 lint 均通过
+你现在的配置写法可以直接用：
+"代码Review": {
+  "type": "skill",
+  "click": "show_window",
+  "agent_mode": "auto",
+  "file_select_mode": "free",
+  "skill_file": "src/skill/代码Review.txt"
+}
+下一步如果你同意，我继续加你提到的第二种交互：在输入框里支持 @文件路径 快速选入（并可删除）。</t>
+  </si>
+  <si>
+    <t>@skills-config.json (2-20) 还需要可以支持配置answer_mode回答模式，Agent还是Ask</t>
+  </si>
+  <si>
+    <t>已支持 answer_mode 配置，skills-config.json 现在可以控制回答模式是 Agent 还是 Ask。
+你可以这样配：
+"步骤1：创建空文件": {
+  "type": "skill",
+  "click": "show_window",
+  "agent_mode": "auto",
+  "answer_mode": "ask",
+  "file_select_mode": "nil",
+  "skill_file": "src/skill/活动开发/步骤一.txt"
+}
+规则是：
+answer_mode: "ask" -&gt; 调用 CLI 时加 --mode ask
+answer_mode: "agent"（或不填）-&gt; 不传 --mode，走默认 Agent 模式
+我已完成的代码变更：
+src/extension.ts
+SkillNode 增加 answerMode
+解析 answer_mode / answerMode
+调用 askCursorAgent(prompt, agentMode, answerMode)
+窗口信息新增“回答模式（answer_mode）”
+src/cursorAgent.ts
+askCursorAgent 增加第三个参数 answerMode
+answerMode 为 ask 时追加 --mode ask
+并且已验证：
+npm run compile 通过
+无 linter 报错</t>
+  </si>
+  <si>
+    <t>@src/extension.ts 是不是可以拆分文件呢？mainwindow单独一个html文件，free文件选择方式单独一个组件，其他的代码留在原位置，或者看看有没有更换的设计方案</t>
+  </si>
+  <si>
+    <t>可以，非常建议拆。你现在的 showSkillWindow 已经同时承担了：
+读配置/读 prompt
+生成整段 HTML/CSS/JS
+维护 Webview 消息协议
+free 选择文件状态管理
+调 Agent 与错误处理
+这就是典型“一个函数太重”，后续每加一种 file_select_mode 都会继续膨胀。
+extension.ts
+Lines 325-540
+async function showSkillWindow(
+  node: SkillNode,
+  extensionPath: string
+): Promise&lt;void&gt; {
+  // ... 读取 skill、创建 panel、拼接大段 HTML/CSS/JS
+  panel.webview.html = `&lt;!DOCTYPE html&gt;
+&lt;html lang="zh-CN"&gt;
+&lt;head&gt;
+  // ... 大量 style
+&lt;/head&gt;
+&lt;body&gt;
+  // ... 大量 UI + script
+&lt;/body&gt;
+&lt;/html&gt;`;
+  // ... onDidReceiveMessage 处理 pick/remove/requestAiAnswer 等
+}
+你提的拆法可行（而且是最稳的）
+你说的方案我建议这样落地：
+resources/webview/mainWindow.html
+只放骨架（header、prompt、answer 区域、容器）
+resources/webview/components/freeFilePicker.html
+放 free 模式 UI 片段（按钮 + 列表）
+resources/webview/mainWindow.js
+前端事件逻辑（按钮点击、渲染 selected files、postMessage）
+src/webview/renderMainWindow.ts
+负责读取 html 模板 + 注入变量（标题、mode、prompt 等）
+src/webview/messageRouter.ts
+处理 pickFiles/removeFile/requestAiAnswer 这些消息
+extension.ts 就只保留：
+config 解析
+showSkillWindow 调用 render + router
+调用 askCursorAgent
+另一个更优设计（如果你后面模式会很多）
+做一个“模式注册表”：
+fileSelectors/free.ts
+fileSelectors/nil.ts
+后续 fileSelectors/workspace.ts、fileSelectors/gitChanged.ts
+统一接口类似：
+render(): string
+onMessage(msg, state): Promise&lt;void&gt;
+这样新增模式时，不需要改主流程。
+结论
+你当前结构可以拆，而且现在正是最佳时机（复杂度刚过临界点）。
+先做你提的“主窗口 html + free 组件”就够了，风险低、收益大。
+如果你同意，我可以下一步给你一版最小拆分目录和接口草图（不改业务行为，只重构结构）。</t>
+  </si>
+  <si>
+    <t>做一个“模式注册表”：
+fileSelectors/free.ts
+fileSelectors/nil.ts
+后续 fileSelectors/workspace.ts、fileSelectors/gitChanged.ts
+统一接口类似：
+render(): string
+onMessage(msg, state): Promise&lt;void&gt;
+这样新增模式时，不需要改主流程。帮我按照最优方案拆，不动功能</t>
+  </si>
+  <si>
+    <t>按你要的“模式注册表”已经拆完，并保持现有功能不变。
+这次重构结果：
+新增 fileSelectors 目录与统一接口
+src/fileSelectors/types.ts
+src/fileSelectors/free.ts
+src/fileSelectors/nil.ts
+src/fileSelectors/registry.ts
+src/extension.ts 改为主流程 + 注册表调度
+根据 file_select_mode 调 getFileSelector(mode)
+UI 区块通过 render() 注入
+前端交互脚本通过 getClientScript() 注入
+Webview 消息先交给 onMessage(msg, state) 处理
+是否要求先选文件由 requiresFiles 控制
+free 行为保持一致
+选择文件/文件夹（可多选）
+文件夹递归展开为文件
+列表展示 + 移除
+nil 行为保持一致
+不渲染选择组件
+不拦截消息
+不要求先选文件
+统一接口（已落地）：
+render(): string
+getClientScript(): string
+onMessage(msg, state): Promise&lt;boolean&gt;
+requiresFiles: boolean
+验证结果：
+npm run compile 通过
+lints 无报错
+你后续要加 workspace.ts / gitChanged.ts 时，只需要新建 selector 文件并在 registry.ts 注册，不需要再动主流程。</t>
+  </si>
+  <si>
+    <t>@src/fileSelectors/registry.ts @src/fileSelectors/types.ts @src/extension.ts 讲一下运行逻辑，文件功能</t>
+  </si>
+  <si>
+    <t>现在这套结构的核心是：extension.ts 负责主流程，registry.ts 负责“按模式选实现”，types.ts 负责“统一协议”。
+src/fileSelectors/types.ts：定义统一接口（协议层）
+这个文件只做一件事：约定每个文件选择模式必须提供什么能力。
+FileSelectorMessage：Webview 发给扩展端的消息结构（如 pickFiles、removeFile）
+FileSelectorState：模式自己的状态，目前是 selectedFiles
+FileSelectorContext：给模式处理函数的上下文（panel + state）
+FileSelectorHandler：统一接口
+mode：模式名（free / nil）
+requiresFiles：执行前是否强制要求有文件
+render()：渲染该模式的 HTML 片段
+getClientScript()：该模式在 Webview 里的前端交互脚本
+onMessage()：扩展端接收消息后的模式处理入口
+src/fileSelectors/registry.ts：模式注册表（选择器工厂）
+这个文件是“路由层”。
+把 free、nil 两个实现注册到 registry
+暴露 getFileSelector(mode?)
+先做 trim + lowerCase
+空值或未知值都回退到 nil
+这样新增模式时（比如 workspace / gitChanged）只要：
+新增文件实现 FileSelectorHandler
+在这里注册一行
+主流程不用改
+src/extension.ts：主流程编排（业务层）
+你现在的运行顺序大致是：
+侧边栏点击技能 -&gt; handleSkillClick
+click === show_window 时进入 showSkillWindow
+读取 skill_file，并读取配置里的 file_select_mode
+调 getFileSelector(fileSelectMode) 取到对应模式实现
+生成主 Webview HTML：
+主框架（标题、skill prompt、执行按钮、回答框）
+模式片段：${fileSelector.render()}
+模式脚本：${fileSelector.getClientScript()}
+onDidReceiveMessage 收消息时先交给模式：
+await fileSelector.onMessage(msg, { panel, state })
+如果返回 true，表示该消息已被模式消费，主流程不再处理
+主流程只处理共性逻辑：
+requestAiAnswer
+requiresFiles 校验（例如 free 必须先选文件）
+组装 prompt（skill 提示词 + 已选文件内容）
+调 askCursorAgent
+回传 aiProgress / aiResult / aiError
+这次拆分后的价值
+扩展性高：新增模式不再碰主流程
+职责清晰：模式 UI/消息在模式文件，AI 调用在主流程
+可维护性高：showSkillWindow 不再写死 free 分支细节
+行为不变：你现有 free、nil 的功能路径保持一致
+如果你愿意，我下一步可以给你补一份 workspace.ts 的最小模板（只列项目文件，不改现有行为），你后面复制就能继续扩展。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">新增一个文件选择器，git_changed，通过项目目录git拉取文件得到文件列表并构建差异diff，参考@e:\GitHubProject\AICodeTools </t>
+  </si>
 </sst>
 </file>
 
@@ -375,18 +894,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -713,7 +1226,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
@@ -737,16 +1250,16 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="6">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="6">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="7">
@@ -755,85 +1268,85 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="8">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0">
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="12" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="14" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="16" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="18" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="20" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="22" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="24" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="26" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="28" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="30" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="34" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -847,7 +1360,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1164,8 +1677,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="3" outlineLevelCol="2"/>
+  <dimension ref="A1:C13"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="85.3636363636364" style="2" customWidth="1"/>
     <col min="2" max="2" width="44.4545454545455" style="2" customWidth="1"/>
@@ -1179,7 +1692,7 @@
       </c>
     </row>
     <row r="2" ht="409.5" spans="1:3">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="2" t="str">
@@ -1203,7 +1716,7 @@
       </c>
     </row>
     <row r="4" ht="322" spans="1:3">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B4" s="2" t="str">
@@ -1212,6 +1725,107 @@
       </c>
       <c r="C4" s="2" t="s">
         <v>6</v>
+      </c>
+    </row>
+    <row r="5" ht="308" spans="1:3">
+      <c r="A5" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="2" t="str">
+        <f>_xlfn.DISPIMG("ID_AB034D59810546E6B8090D478F91EFAD",1)</f>
+        <v>=DISPIMG("ID_AB034D59810546E6B8090D478F91EFAD",1)</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" ht="266" spans="1:3">
+      <c r="A6" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="2" t="str">
+        <f>_xlfn.DISPIMG("ID_9007E9C07C77434B99BD21BA91A8210E",1)</f>
+        <v>=DISPIMG("ID_9007E9C07C77434B99BD21BA91A8210E",1)</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" ht="336" spans="1:3">
+      <c r="A7" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" s="2" t="str">
+        <f>_xlfn.DISPIMG("ID_A9BAFE5D8A55439995DC98BD6BE7FC44",1)</f>
+        <v>=DISPIMG("ID_A9BAFE5D8A55439995DC98BD6BE7FC44",1)</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" ht="409.5" spans="1:3">
+      <c r="A8" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" s="2" t="str">
+        <f>_xlfn.DISPIMG("ID_8CB55B8CEF6F4AC9A38D8AF353DB8794",1)</f>
+        <v>=DISPIMG("ID_8CB55B8CEF6F4AC9A38D8AF353DB8794",1)</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" ht="409.5" spans="1:3">
+      <c r="A9" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" s="2" t="str">
+        <f>_xlfn.DISPIMG("ID_42D4C69B06DB45018FE4A5B9EC5ACAFA",1)</f>
+        <v>=DISPIMG("ID_42D4C69B06DB45018FE4A5B9EC5ACAFA",1)</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" ht="409.5" spans="1:3">
+      <c r="A10" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" s="2" t="str">
+        <f>_xlfn.DISPIMG("ID_CE1FF791048D4A9C9C815BE270F81F3C",1)</f>
+        <v>=DISPIMG("ID_CE1FF791048D4A9C9C815BE270F81F3C",1)</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="11" ht="409.5" spans="1:3">
+      <c r="A11" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B11" s="2" t="str">
+        <f>_xlfn.DISPIMG("ID_70BA1EE1FEF1472FB099100E5566212D",1)</f>
+        <v>=DISPIMG("ID_70BA1EE1FEF1472FB099100E5566212D",1)</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="12" s="2" customFormat="1" ht="409.5" spans="1:3">
+      <c r="A12" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B12" s="2" t="str">
+        <f>_xlfn.DISPIMG("ID_0E58F2BB651D4ECFB462F5288FECD91A",1)</f>
+        <v>=DISPIMG("ID_0E58F2BB651D4ECFB462F5288FECD91A",1)</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="13" ht="28" spans="1:3">
+      <c r="A13" s="2" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>

--- a/vibecoding.xlsx
+++ b/vibecoding.xlsx
@@ -349,11 +349,40 @@
       </xdr:spPr>
     </xdr:pic>
   </etc:cellImage>
+  <etc:cellImage>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="13" name="ID_09A0E65A342C4011A083B79EF3F6025A"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId12"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5962650" y="51358800"/>
+          <a:ext cx="5181600" cy="13487400"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+  </etc:cellImage>
 </etc:cellImages>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
   <si>
     <t>AI记录</t>
   </si>
@@ -722,6 +751,41 @@
   </si>
   <si>
     <t xml:space="preserve">新增一个文件选择器，git_changed，通过项目目录git拉取文件得到文件列表并构建差异diff，参考@e:\GitHubProject\AICodeTools </t>
+  </si>
+  <si>
+    <t>已完成，新增了 git_changed 文件选择器，并接入了模式注册表，保持现有功能不变。
+你现在可以这样配置
+在 skills-config.json 里用：
+"file_select_mode": "git_changed"
+我做的改动
+新增 src/fileSelectors/gitChanged.ts
+通过 git status --short 拉取变更文件列表
+通过 git diff HEAD -- &lt;file&gt; 构建 diff
+对未跟踪文件（??）直接读取文件内容，按“新增文件”格式拼接
+支持刷新按钮 刷新 Git 变更
+自动把结果写入 selector state：
+selectedFiles：变更文件列表
+promptOverride：分支 + 文件列表 + diff 文本
+更新 src/fileSelectors/registry.ts
+注册 git_changed 模式
+更新 src/fileSelectors/types.ts
+FileSelectorState 新增 promptOverride?: string
+更新 src/extension.ts
+发送前增加优先逻辑：
+有 promptOverride 就用它（前面仍拼接 skill_file 提示词）
+否则继续走原本 buildAgentPrompt（free/nil 不受影响）
+运行行为（git_changed）
+打开技能窗口后，自动触发一次 Git 变更刷新
+显示当前变更文件列表
+点击“执行技能”时，发送内容包含：
+skill_file 的提示词
+当前分支
+变更文件清单
+Git diff 内容
+编译和检查已通过：
+npm run compile ✅
+lints ✅
+如果你要，我下一步可以给 git_changed 再加一个配置项（例如 git_changed_scope）支持只看某个目录或只看特定后缀文件。</t>
   </si>
 </sst>
 </file>
@@ -1350,7 +1414,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1362,9 +1426,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1740,7 +1801,7 @@
       </c>
     </row>
     <row r="6" ht="266" spans="1:3">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B6" s="2" t="str">
@@ -1823,9 +1884,16 @@
         <v>22</v>
       </c>
     </row>
-    <row r="13" ht="28" spans="1:3">
+    <row r="13" ht="409.5" spans="1:3">
       <c r="A13" s="2" t="s">
         <v>23</v>
+      </c>
+      <c r="B13" s="2" t="str">
+        <f>_xlfn.DISPIMG("ID_09A0E65A342C4011A083B79EF3F6025A",1)</f>
+        <v>=DISPIMG("ID_09A0E65A342C4011A083B79EF3F6025A",1)</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
   </sheetData>
